--- a/docs/评估集.xlsx
+++ b/docs/评估集.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="2"/>
@@ -3524,6 +3524,196 @@
       <c r="I61" s="6" t="inlineStr">
         <is>
           <t>边界：已知缺口</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>分析浦东近两期，如果降了就查原因，没降就看看它和同档平均水平比怎么样</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2025Q3 上海浦东国际机场 4.23；2025Q4 上海浦东国际机场 4.23；两期持平（没降）；同档平均 4.13；上海浦东国际机场 比同档平均 高 0.1</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2025Q4-P09 / 2025Q4-P18</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>★ 带条件：该判降没降，再只走【它走到的那一支】。★ 期望答案由 AI 起草、待用户审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>浦东2025Q4表现怎么样，要是不好就说说是哪一项拖后腿</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2025Q4 上海浦东国际机场 综合得分 4.23；排名第 5；★ 并【说清】「要是不好就说说是哪一项拖后腿」这一件【没答】——那一件该出声，不该静默（AI 起草、待用户审）</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>★ 条件藏在字缝里（没有“如果”两字）。★ “哪一项拖后腿”这一件【答不了】—— 该【说出来】，不该静默。期望答案由 AI 起草、待审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>浦东和虹桥2025Q4谁高，低的那家差在哪</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>上海浦东国际机场 4.23；上海虹桥国际机场 4.25；上海虹桥国际机场 更高（4.25 比 4.23）</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>★ 要先算出来才知道“低的那家”指谁——句子里没有“如果”，可它照样是岔路口。★ 期望答案由 AI 起草、待审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>浦东2025Q4综合得分是多少</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2025Q4 上海浦东国际机场 综合得分 4.23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>★★ 反向题：问一个数，【不该】走任何条件分支、不该展开。★ 没有它，一个“什么都当条件处理”的实现也能把前几道蒙对。期望答案由 AI 起草、待审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>浦东2025Q4排第几，前三名是谁</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>上海浦东国际机场 排名第 5；前三名：北京大兴国际机场 4.28、深圳宝安国际机场 4.27、上海虹桥国际机场 4.25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>★ 两步、不是分支——两件都必然要答。★ 而实测主链答不了“前三名” → 该【说出来】。期望答案由 AI 起草、待审。</t>
         </is>
       </c>
     </row>

--- a/docs/评估集.xlsx
+++ b/docs/评估集.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="2"/>
@@ -3714,6 +3714,170 @@
       <c r="I66" t="inlineStr">
         <is>
           <t>★ 两步、不是分支——两件都必然要答。★ 而实测主链答不了“前三名” → 该【说出来】。期望答案由 AI 起草、待审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025Q4合肥新桥国际机场排第几，最后一名是谁</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>合肥新桥国际机场 排名第 39；最后一名（第42名）太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>★ 两步、两件都必然要答。★ 第二件【要去补】,不该只说「我没答」。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025Q3广州白云国际机场综合得分是多少，排名第几</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2025Q3 广州白云国际机场 综合得分 4.21；排名第 9</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2025Q3-P09</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>★ 两件都在同一句里,而一件是【数值】、一件是【排名】—— 看它能不能两件都做。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>叙述·检索</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025Q4分吞吐量级服务测评里，4000万级以上机场综合得分第一是谁</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>检索</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>北京大兴国际机场 4.28（2025Q4 4000万级以上机场综合得分第一）</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>chunk=2025Q4-P18</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>★★ 假复合 —— 逗号【不是分句】,前半段「2025Q4分吞吐量级服务测评里」是【状语】。★ 补漏【不该】把它当成一件去补,也不该报「漏了」。#48 就是这个形状的误报。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>浦东和虹桥2025Q4谁高，各自排第几</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>上海虹桥国际机场 4.25 高于 上海浦东国际机场 4.23；虹桥排第 3、浦东排第 5</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>★ 第二段「各自排第几」【不带机场名】—— 得靠第一段继承。★ 测补漏时的【参数传承】。（AI 起草、待用户审）</t>
         </is>
       </c>
     </row>

--- a/docs/评估集.xlsx
+++ b/docs/评估集.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="2"/>
@@ -3751,7 +3751,6 @@
           <t>2025Q4-P09</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>★ 两步、两件都必然要答。★ 第二件【要去补】,不该只说「我没答」。（AI 起草、待用户审）</t>
@@ -3792,7 +3791,6 @@
           <t>2025Q3-P09</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>★ 两件都在同一句里,而一件是【数值】、一件是【排名】—— 看它能不能两件都做。（AI 起草、待用户审）</t>
@@ -3833,7 +3831,6 @@
           <t>chunk=2025Q4-P18</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>★★ 假复合 —— 逗号【不是分句】,前半段「2025Q4分吞吐量级服务测评里」是【状语】。★ 补漏【不该】把它当成一件去补,也不该报「漏了」。#48 就是这个形状的误报。（AI 起草、待用户审）</t>
@@ -3874,10 +3871,50 @@
           <t>2025Q4-P09</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>★ 第二段「各自排第几」【不带机场名】—— 得靠第一段继承。★ 测补漏时的【参数传承】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>比较北京大兴和上海浦东2025Q3和2025Q4的综合得分变化，如果下降了就去找原因</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>北京大兴国际机场 4.3 → 4.28（下降了）；上海浦东国际机场 4.23 → 4.23（持平）。所以只有北京大兴下降</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2025Q3-P09 | 2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>★★ 多步 + 条件 —— 触发点在第3步:那时结果里已有【两步】,而条件里的两个量来自【第1步的两条】。★ 现有所有条件题的判据场景都是"两个量来自两个不同步骤",这一道撞那个缺口。（AI 起草、待用户审）</t>
         </is>
       </c>
     </row>

--- a/docs/评估集.xlsx
+++ b/docs/评估集.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="2"/>
@@ -3911,10 +3911,569 @@
           <t>2025Q3-P09 | 2025Q4-P09</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>★★ 多步 + 条件 —— 触发点在第3步:那时结果里已有【两步】,而条件里的两个量来自【第1步的两条】。★ 现有所有条件题的判据场景都是"两个量来自两个不同步骤",这一道撞那个缺口。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>72</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>三亚凤凰国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>73</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>上海浦东国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>74</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>上海虹桥国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>75</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>乌鲁木齐天山国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>76</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>北京大兴国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>77</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>北京首都国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>南京禄口国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>南宁吴圩国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>兰州中川国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>兰州中川国际机场 2025Q4 一级指标里最低的是「航班不正常保障」2.88</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>81</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>呼和浩特白塔国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>呼和浩特白塔国际机场 2025Q4 一级指标里最低的是「航班不正常保障」2.91</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>82</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>哈尔滨太平国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>哈尔滨太平国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.02</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>83</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>宁波栎社国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>宁波栎社国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.05</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>84</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>成都天府国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>成都天府国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.18</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>85</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>昆明长水国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>昆明长水国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.09</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>86</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>杭州萧山国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>杭州萧山国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.25</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>87</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>郑州新郑国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>郑州新郑国际机场 2025Q4 一级指标里最低的是「航班不正常保障」2.93</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
         </is>
       </c>
     </row>

--- a/docs/评估集.xlsx
+++ b/docs/评估集.xlsx
@@ -2956,7 +2956,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>2025Q4分吞吐量级服务测评里，4000万级以上机场综合得分前两名是谁</t>
+          <t>2025Q4分吞吐量级服务测评报告里，4000万级以上机场那几页的红色和蓝色代表什么</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>北京大兴国际机场4.28；深圳宝安国际机场4.27。</t>
+          <t>红色为高于行业平均分，蓝色为低于行业平均分，下同。</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -2977,7 +2977,14 @@
       <c r="H47" s="6" t="n"/>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>检索：分吞吐量级文本</t>
+          <t>检索：分吞吐量级表格的【排版约定】—— 红=高于行业平均分,蓝=低于行业平均分。
+★ 这条【只能从原文读】:库里的 机场分档 表有档位和平均分,
+  但没有"红色/蓝色代表什么"(那是"这张表怎么读"的说明)。
+★ 改动理由(2026-10-01):原来问的是"4000万级以上前两名是谁",
+  而那个【库里能算】—— 考检索是白考。换成这一句,它才重新变成能区分好坏的题。
+⚠ 问法是【验过的】:route 走检索 ✓ · 检索命中 2025Q4-P18 ✓ · 答案取回了那一句 ✓
+  ★ 前两版问法都踩了坑(一版判"判不出"、一版被推去走 SQL),原因都是
+    "只验了这句话只有原文里有,没验系统能不能走到那儿"。</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2997,7 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>叙述·检索</t>
+          <t>数值·排名</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -3000,7 +3007,7 @@
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>检索</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -3016,7 +3023,11 @@
       <c r="H48" s="6" t="n"/>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>检索：分吞吐量级文本</t>
+          <t>检索：分吞吐量级文本
+★ 2026-10-01 改:期望去向 检索→SQL,类别 叙述·检索→数值·排名。
+理由:这题问的是"某一档里第一是谁",而库里有 `机场分档` 表(4 个档),
+SQL 能直接算出来。★ 检索那条路拿到的是一串孤立数字(表格结构丢了),
+配不上对。★ 判据:「能算的地方,别去检索里翻」。</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3040,7 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>叙述·检索</t>
+          <t>数值·排名</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -3039,7 +3050,7 @@
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>检索</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -3055,7 +3066,11 @@
       <c r="H49" s="6" t="n"/>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>检索：分吞吐量级并列</t>
+          <t>检索：分吞吐量级并列
+★ 2026-10-01 改:期望去向 检索→SQL,类别 叙述·检索→数值·排名。
+理由:这题问的是"某一档里第一是谁",而库里有 `机场分档` 表(4 个档),
+SQL 能直接算出来。★ 检索那条路拿到的是一串孤立数字(表格结构丢了),
+配不上对。★ 判据:「能算的地方,别去检索里翻」。</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>叙述·检索</t>
+          <t>数值·排名</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,7 +3833,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>检索</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3833,7 +3848,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>★★ 假复合 —— 逗号【不是分句】,前半段「2025Q4分吞吐量级服务测评里」是【状语】。★ 补漏【不该】把它当成一件去补,也不该报「漏了」。#48 就是这个形状的误报。（AI 起草、待用户审）</t>
+          <t>★★ 假复合 —— 逗号【不是分句】,前半段「2025Q4分吞吐量级服务测评里」是【状语】。★ 补漏【不该】把它当成一件去补,也不该报「漏了」。#48 就是这个形状的误报。（AI 起草、待用户审）
+★ 2026-10-01 改:期望去向 检索→SQL,类别 叙述·检索→数值·排名。
+理由:这题问的是"某一档里第一是谁",而库里有 `机场分档` 表(4 个档),
+SQL 能直接算出来。★ 检索那条路拿到的是一串孤立数字(表格结构丢了),
+配不上对。★ 判据:「能算的地方,别去检索里翻」。</t>
         </is>
       </c>
     </row>

--- a/docs/评估集.xlsx
+++ b/docs/评估集.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="2"/>
@@ -4493,6 +4493,54 @@
       <c r="I87" t="inlineStr">
         <is>
           <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>88</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>补充</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>数值·单点</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025Q3的上一期上海浦东综合得分是多少</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2025Q2 上海浦东国际机场：4.22</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>表=综合得分;期次=2025Q2;机场=上海浦东国际机场</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>相对说法 + 句子里自己写的期次。
+★★ 2026-10-02 张君杰出的一道题,而他【预判了它会错】:
+   「你会抽取期次2025Q3而不是2025Q2,因为明确期次优先于推断期次」。
+★ 实测他预判对了(而实际更坏:有具体机场时它【安静地答了 2025Q3】,
+   连"我理解成 2025Q3 了"都不说 —— 静默失败)。
+★ 根因两处:① 推期次 只看记忆里的参照,不看【这一句自己写的期次】
+            ② ask 那条路【只抽不推】(agent 有推期次)
+★ 修法:两处都改;优先级统一成「推期次优先」(它只在识别到相对说法时才有值)。
+⚠ 加这道题是为了让它【以后被弄坏了,分数会掉】—— 之前它没有测试覆盖。</t>
         </is>
       </c>
     </row>

--- a/docs/评估集.xlsx
+++ b/docs/评估集.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="2"/>
@@ -4541,6 +4541,94 @@
             ② ask 那条路【只抽不推】(agent 有推期次)
 ★ 修法:两处都改;优先级统一成「推期次优先」(它只在识别到相对说法时才有值)。
 ⚠ 加这道题是为了让它【以后被弄坏了,分数会掉】—— 之前它没有测试覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>89</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>补充</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>数值·比较</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2025Q3和上一期上海浦东综合得分谁高</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2025Q3 上海浦东国际机场：4.23；2025Q2 上海浦东国际机场：4.22；2025Q3 更高</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>表=综合得分;期次=2025Q3;机场=上海浦东国际机场 | 表=综合得分;期次=2025Q2;机场=上海浦东国际机场</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>★ 2026-10-02 加。★ 它和「2025Q3的上一期上海浦东综合得分是多少」【长得几乎一样】,
+而【2025Q3 的角色完全不同】:
+   「2025Q3 的上一期」 → 2025Q3 是【参照】   → 只查 2025Q2
+   「2025Q3 和上一期」 → 2025Q3 是【对象之一】→ 查 2025Q3 和 2025Q2
+★ 这两句必须都在,否则"只改了一半"照不出来。
+★ 判据(能算的):期次后面紧跟「的」+关系词 → 参照;由「和/与/跟」连接 → 对象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>90</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>补充</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>数值·比较</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2025Q3的下一期上海浦东综合得分是多少</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2025Q4 上海浦东国际机场：4.23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>表=综合得分;期次=2025Q4;机场=上海浦东国际机场</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>★ 2026-10-02 加。「下一期」是「上一期」的【镜像】——
+  以前加它是一次打补丁(那条分支只认自己的词);
+  ★★ 而有了期次计划(第3层判出 relation=compare_with_next),
+     第2层补的只是【那个方向的另一格】,不是"又一个说法"。</t>
         </is>
       </c>
     </row>
